--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/ARIZONA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/ARIZONA_2012.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C121">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C194">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C623">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C678">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1014">
